--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -709,7 +709,7 @@
     <t>411</t>
   </si>
   <si>
-    <t>Intermédiaire de placement social</t>
+    <t>Services accompagnement TDC et ADB</t>
   </si>
   <si>
     <t>412</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J55-CategorieEG-ROR.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
